--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_11.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_11.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>NeuroType</t>
+          <t>IV2</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>IQ</t>
+          <t>Perfectionism</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-2.532211781198142</v>
+        <v>0.9470974954347653</v>
       </c>
       <c r="C2">
-        <v>-1.869195398755156</v>
+        <v>-1.056017899087587</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.8872987712903826</v>
+        <v>0.4996408082198968</v>
       </c>
       <c r="C3">
-        <v>0.2326156723734831</v>
+        <v>-0.1346975438638276</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>1.306062514815028</v>
+        <v>0.7054305111700935</v>
       </c>
       <c r="C4">
-        <v>1.125468613822324</v>
+        <v>0.9423180976345067</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>0.5998062733691747</v>
+        <v>-0.5765288433378574</v>
       </c>
       <c r="C5">
-        <v>0.7038501905435168</v>
+        <v>-1.342920927244171</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>0.03172619392400194</v>
+        <v>0.1634565931276744</v>
       </c>
       <c r="C6">
-        <v>0.2815698946551519</v>
+        <v>-1.022243523501747</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>1.033361237708021</v>
+        <v>-0.1801363285866524</v>
       </c>
       <c r="C7">
-        <v>0.6633729656946807</v>
+        <v>-0.2054285827489791</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>-0.01615061311935909</v>
+        <v>0.09011726544424455</v>
       </c>
       <c r="C8">
-        <v>0.01617253940447125</v>
+        <v>0.9963235305404006</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.2483163478191818</v>
+        <v>0.9504662725814893</v>
       </c>
       <c r="C9">
-        <v>-1.929232635580403</v>
+        <v>0.1087349503681881</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.1104388830787071</v>
+        <v>-0.5876845283332545</v>
       </c>
       <c r="C10">
-        <v>-0.1028820120317346</v>
+        <v>-0.2898064956083008</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.3041767891140004</v>
+        <v>-0.8847408704532918</v>
       </c>
       <c r="C11">
-        <v>1.140504141931852</v>
+        <v>0.2258887201715426</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-2.450919691334028</v>
+        <v>2.124191164249319</v>
       </c>
       <c r="C12">
-        <v>-1.178094746281675</v>
+        <v>-1.046736840280199</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.8261370641569621</v>
+        <v>0.4167546342125771</v>
       </c>
       <c r="C13">
-        <v>-0.9520570110008313</v>
+        <v>0.08471206281850968</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-1.428965020973028</v>
+        <v>0.272458507655589</v>
       </c>
       <c r="C14">
-        <v>0.01847991417548567</v>
+        <v>-1.318519234857362</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.6027786873592741</v>
+        <v>0.5580451094835496</v>
       </c>
       <c r="C15">
-        <v>-1.757577977860326</v>
+        <v>-1.121016963717457</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>0.2596380005398026</v>
+        <v>-1.997431355194276</v>
       </c>
       <c r="C16">
-        <v>1.069962651602407</v>
+        <v>0.771245333305163</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>-1.699259635706469</v>
+        <v>0.8639127255907058</v>
       </c>
       <c r="C17">
-        <v>-0.7385872438275827</v>
+        <v>0.2291417846691337</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>-0.3646242701809866</v>
+        <v>1.361424996010841</v>
       </c>
       <c r="C18">
-        <v>-0.1012958272008682</v>
+        <v>-0.2618104067180613</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-0.04617982565317591</v>
+        <v>1.360263841918098</v>
       </c>
       <c r="C19">
-        <v>-0.1353396575712555</v>
+        <v>-0.5961500225672378</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>-1.056004934358724</v>
+        <v>1.451814466918674</v>
       </c>
       <c r="C20">
-        <v>-1.285953258939398</v>
+        <v>1.091783227706214</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>-1.593319621024712</v>
+        <v>0.8592769633437629</v>
       </c>
       <c r="C21">
-        <v>-0.02668901473634988</v>
+        <v>0.415672672464921</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>-0.02712123257361379</v>
+        <v>-0.5158245529517579</v>
       </c>
       <c r="C22">
-        <v>-0.3607995646900922</v>
+        <v>1.092575095795991</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>1.139811248570995</v>
+        <v>-1.141140669130519</v>
       </c>
       <c r="C23">
-        <v>2.105231616637383</v>
+        <v>0.3986479228313934</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.3720689515396774</v>
+        <v>-0.4049416651098768</v>
       </c>
       <c r="C24">
-        <v>0.2005705979245798</v>
+        <v>0.9499852796970177</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.007186998672760672</v>
+        <v>1.338534361612494</v>
       </c>
       <c r="C25">
-        <v>0.6131528550239962</v>
+        <v>-2.002127875098854</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-0.08342586637843481</v>
+        <v>0.124014672517777</v>
       </c>
       <c r="C26">
-        <v>-0.9311121486811472</v>
+        <v>-0.1218944563504086</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.1347032032377199</v>
+        <v>-0.2693739423454838</v>
       </c>
       <c r="C27">
-        <v>0.4364863569707748</v>
+        <v>-1.116967528428803</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.7643239976796145</v>
+        <v>0.1536092138858353</v>
       </c>
       <c r="C28">
-        <v>1.390377564385778</v>
+        <v>0.8854099093453187</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>1.043507451393142</v>
+        <v>1.393603829230746</v>
       </c>
       <c r="C29">
-        <v>-0.3011731095941477</v>
+        <v>-1.203508002153912</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>-0.04387830885275033</v>
+        <v>0.07264072012179165</v>
       </c>
       <c r="C30">
-        <v>-0.3784752101166831</v>
+        <v>-1.662419532983631</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>0.8352357480724868</v>
+        <v>0.09708255122625012</v>
       </c>
       <c r="C31">
-        <v>1.781848032036272</v>
+        <v>-0.1490716433449665</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>0.7116632927097188</v>
+        <v>0.5984599182392926</v>
       </c>
       <c r="C32">
-        <v>-1.720370158759986</v>
+        <v>0.2295934323970519</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.3165522482877287</v>
+        <v>-0.6184715936293264</v>
       </c>
       <c r="C33">
-        <v>-0.8331513871909082</v>
+        <v>0.8647380359746821</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.9820055025331802</v>
+        <v>0.6939989577269846</v>
       </c>
       <c r="C34">
-        <v>1.647975226469405</v>
+        <v>0.7212871228008175</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-1.983998511474097</v>
+        <v>0.2834829655612153</v>
       </c>
       <c r="C35">
-        <v>-0.6688268205105821</v>
+        <v>1.776246074001787</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>0.02786988015560909</v>
+        <v>-1.783780224168972</v>
       </c>
       <c r="C36">
-        <v>-0.3035953131181082</v>
+        <v>0.03565689502975811</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>0.8962101119337645</v>
+        <v>-0.4133569944241872</v>
       </c>
       <c r="C37">
-        <v>1.701694205347924</v>
+        <v>0.07919317217773895</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.4916957010739228</v>
+        <v>-1.948825635772306</v>
       </c>
       <c r="C38">
-        <v>-0.4550548274307631</v>
+        <v>2.5956327843458</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>0.04477221859472243</v>
+        <v>-0.6378726839383568</v>
       </c>
       <c r="C39">
-        <v>0.08621627488258524</v>
+        <v>-1.508518731369053</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-2.131752910342836</v>
+        <v>0.8587213922958001</v>
       </c>
       <c r="C40">
-        <v>-2.889924045246925</v>
+        <v>0.5167065266745541</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.03726676351122992</v>
+        <v>-0.01046408843403691</v>
       </c>
       <c r="C41">
-        <v>0.6400976506440436</v>
+        <v>-0.9687885515591538</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>0.2467993598311418</v>
+        <v>-0.1563198103526527</v>
       </c>
       <c r="C42">
-        <v>-1.952296448281784</v>
+        <v>-1.010046142485027</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-1.275695422528029</v>
+        <v>0.5330610029562752</v>
       </c>
       <c r="C43">
-        <v>-2.074779652865098</v>
+        <v>-1.321250753752465</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>1.115956780283829</v>
+        <v>-1.240566533342968</v>
       </c>
       <c r="C44">
-        <v>-0.02428329173673804</v>
+        <v>0.4360863208512329</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>-0.1019432535945388</v>
+        <v>0.3577372219192996</v>
       </c>
       <c r="C45">
-        <v>0.7023726869075079</v>
+        <v>-0.4249529525848945</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.8144485272727314</v>
+        <v>0.3915488061741006</v>
       </c>
       <c r="C46">
-        <v>-1.262553880383312</v>
+        <v>1.473938026098672</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>-1.731392349540707</v>
+        <v>0.4258866810357088</v>
       </c>
       <c r="C47">
-        <v>0.5013298428476565</v>
+        <v>-1.01857597866219</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>-0.4402495002358189</v>
+        <v>-0.8784107804466907</v>
       </c>
       <c r="C48">
-        <v>-0.6016262192285901</v>
+        <v>-1.875984574925937</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.1947227293249003</v>
+        <v>-0.8595874511381595</v>
       </c>
       <c r="C49">
-        <v>-1.233354867961987</v>
+        <v>-0.2442592914188836</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>1.008260715651631</v>
+        <v>0.5353912902864065</v>
       </c>
       <c r="C50">
-        <v>0.2174778134282923</v>
+        <v>-1.984182586075006</v>
       </c>
     </row>
     <row r="51">
@@ -1015,660 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.1621877642948465</v>
+        <v>0.5811156211044611</v>
       </c>
       <c r="C51">
-        <v>-0.09269027997787184</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="B52">
-        <v>1.114810424532134</v>
-      </c>
-      <c r="C52">
-        <v>0.8971195312744392</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>52</t>
-        </is>
-      </c>
-      <c r="B53">
-        <v>0.1823207042540592</v>
-      </c>
-      <c r="C53">
-        <v>1.445174985863563</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="B54">
-        <v>0.5829872342500231</v>
-      </c>
-      <c r="C54">
-        <v>0.9152318346560416</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
-      <c r="B55">
-        <v>0.4346335496020616</v>
-      </c>
-      <c r="C55">
-        <v>0.1214272001273771</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="B56">
-        <v>-0.2345707016615899</v>
-      </c>
-      <c r="C56">
-        <v>-0.002502150365761013</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="B57">
-        <v>0.7354827171949038</v>
-      </c>
-      <c r="C57">
-        <v>-0.6613605834068923</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="B58">
-        <v>-0.711578005568746</v>
-      </c>
-      <c r="C58">
-        <v>-0.8050999388173008</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="B59">
-        <v>0.0180042250091639</v>
-      </c>
-      <c r="C59">
-        <v>0.01790999397453122</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="B60">
-        <v>0.08948140299915473</v>
-      </c>
-      <c r="C60">
-        <v>0.3517066271528923</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="B61">
-        <v>0.1283553910205301</v>
-      </c>
-      <c r="C61">
-        <v>1.152402030854099</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="B62">
-        <v>0.8789393702699131</v>
-      </c>
-      <c r="C62">
-        <v>0.02625044704067875</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="B63">
-        <v>0.8329241005751242</v>
-      </c>
-      <c r="C63">
-        <v>-1.194427464726285</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="B64">
-        <v>0.1519685182568677</v>
-      </c>
-      <c r="C64">
-        <v>-0.897021179143641</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="B65">
-        <v>-0.2217540579196924</v>
-      </c>
-      <c r="C65">
-        <v>0.08336188617178052</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="B66">
-        <v>1.1312897139504</v>
-      </c>
-      <c r="C66">
-        <v>0.8204007241715545</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="B67">
-        <v>-0.9664739238664098</v>
-      </c>
-      <c r="C67">
-        <v>-1.499546126546089</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="B68">
-        <v>1.743942588867615</v>
-      </c>
-      <c r="C68">
-        <v>0.8022887875127679</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="B69">
-        <v>0.9057996095010019</v>
-      </c>
-      <c r="C69">
-        <v>0.8769040126193373</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="B70">
-        <v>-0.03392406994644429</v>
-      </c>
-      <c r="C70">
-        <v>0.8487107077149971</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="B71">
-        <v>0.2917907525013808</v>
-      </c>
-      <c r="C71">
-        <v>0.1004348448950879</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="B72">
-        <v>0.2489984763763439</v>
-      </c>
-      <c r="C72">
-        <v>1.590931916858062</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="B73">
-        <v>0.1182225886766888</v>
-      </c>
-      <c r="C73">
-        <v>1.664210248539689</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="B74">
-        <v>0.8917880624375397</v>
-      </c>
-      <c r="C74">
-        <v>0.7237796438928716</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="B75">
-        <v>-1.84063907565942</v>
-      </c>
-      <c r="C75">
-        <v>-0.9817628713774733</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="B76">
-        <v>0.7919815214506097</v>
-      </c>
-      <c r="C76">
-        <v>-0.492807859947619</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="B77">
-        <v>-0.6333288635039439</v>
-      </c>
-      <c r="C77">
-        <v>0.5853113534635896</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="B78">
-        <v>0.3917414138256288</v>
-      </c>
-      <c r="C78">
-        <v>-0.2920003842633004</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="B79">
-        <v>0.4037765539278076</v>
-      </c>
-      <c r="C79">
-        <v>1.81080000112763</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="B80">
-        <v>-0.9255136468758816</v>
-      </c>
-      <c r="C80">
-        <v>0.2320798341729434</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="B81">
-        <v>-0.4579065056482289</v>
-      </c>
-      <c r="C81">
-        <v>0.05212282799313514</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="B82">
-        <v>1.954897863779594</v>
-      </c>
-      <c r="C82">
-        <v>1.490925550380383</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>82</t>
-        </is>
-      </c>
-      <c r="B83">
-        <v>-0.9629833865369001</v>
-      </c>
-      <c r="C83">
-        <v>0.248493726031692</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="B84">
-        <v>1.533439517582604</v>
-      </c>
-      <c r="C84">
-        <v>1.653735824877522</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="B85">
-        <v>-2.834327307707745</v>
-      </c>
-      <c r="C85">
-        <v>-0.2680011748485942</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="B86">
-        <v>-0.2599694372864035</v>
-      </c>
-      <c r="C86">
-        <v>-0.4652734942613132</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="B87">
-        <v>-0.5373137745758033</v>
-      </c>
-      <c r="C87">
-        <v>-0.0188791980007498</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>87</t>
-        </is>
-      </c>
-      <c r="B88">
-        <v>-0.4483224772131479</v>
-      </c>
-      <c r="C88">
-        <v>-1.467936614573915</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>88</t>
-        </is>
-      </c>
-      <c r="B89">
-        <v>1.013434956671655</v>
-      </c>
-      <c r="C89">
-        <v>2.267838817101041</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>89</t>
-        </is>
-      </c>
-      <c r="B90">
-        <v>-1.077142203087534</v>
-      </c>
-      <c r="C90">
-        <v>-0.141896409884154</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="B91">
-        <v>0.8657420818071374</v>
-      </c>
-      <c r="C91">
-        <v>0.8862868808868958</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>91</t>
-        </is>
-      </c>
-      <c r="B92">
-        <v>-1.915450123976082</v>
-      </c>
-      <c r="C92">
-        <v>0.05979987550677734</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>92</t>
-        </is>
-      </c>
-      <c r="B93">
-        <v>1.339509693477878</v>
-      </c>
-      <c r="C93">
-        <v>1.036193479458719</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>93</t>
-        </is>
-      </c>
-      <c r="B94">
-        <v>0.9618633472834267</v>
-      </c>
-      <c r="C94">
-        <v>0.8435552041434828</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>94</t>
-        </is>
-      </c>
-      <c r="B95">
-        <v>-0.7827068835511013</v>
-      </c>
-      <c r="C95">
-        <v>-0.3438100134844429</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>95</t>
-        </is>
-      </c>
-      <c r="B96">
-        <v>-0.3579843316267311</v>
-      </c>
-      <c r="C96">
-        <v>-0.4902841728334393</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>96</t>
-        </is>
-      </c>
-      <c r="B97">
-        <v>1.521498775104953</v>
-      </c>
-      <c r="C97">
-        <v>-0.5040737745543874</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>97</t>
-        </is>
-      </c>
-      <c r="B98">
-        <v>0.5780653374468447</v>
-      </c>
-      <c r="C98">
-        <v>-0.02120183557373906</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="B99">
-        <v>0.5273681684105386</v>
-      </c>
-      <c r="C99">
-        <v>-0.6851761655176281</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="B100">
-        <v>-0.3640116487013612</v>
-      </c>
-      <c r="C100">
-        <v>0.9404642885002028</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="B101">
-        <v>0.6105390704868034</v>
-      </c>
-      <c r="C101">
-        <v>-0.1701337099445006</v>
+        <v>-0.1106285187333239</v>
       </c>
     </row>
   </sheetData>
